--- a/02_DIA_inicio_2026_analisis_assets/rbd_9433_escuela-basica-pablo-neruda_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9433_escuela-basica-pablo-neruda_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17A6355F-E08C-43F8-9ACA-7BE1EF7ED377}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{586EB55D-EFD3-4303-B963-C829FCBD80CE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{453621FC-F25F-433B-9840-757D1682E5C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC950B9B-E3F5-4A20-BD0B-6D330798E042}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6959168D-C705-4C5B-A8C9-F25C15A971B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B2DE30E-C50D-4D18-B382-D14D739C97F6}"/>
 </file>